--- a/Result/profitability/2423.xlsx
+++ b/Result/profitability/2423.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7637499999999999</v>
+        <v>0.8425</v>
       </c>
       <c r="N2" t="n">
-        <v>52.12125</v>
+        <v>52.6875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7500000000000001</v>
+        <v>0.795</v>
       </c>
       <c r="N3" t="n">
-        <v>51.41875</v>
+        <v>51.78125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0.68625</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>50.64625</v>
+        <v>50.97875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6275000000000001</v>
+        <v>0.71125</v>
       </c>
       <c r="N5" t="n">
-        <v>49.04</v>
+        <v>49.0175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.58625</v>
+        <v>0.6375000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>48.14624999999999</v>
+        <v>48.57625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4962500000000001</v>
+        <v>0.53</v>
       </c>
       <c r="N7" t="n">
-        <v>47.19</v>
+        <v>47.6375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.45625</v>
+        <v>0.44375</v>
       </c>
       <c r="N8" t="n">
-        <v>46.28375</v>
+        <v>46.1775</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.34875</v>
       </c>
       <c r="N10" t="n">
-        <v>45.17999999999999</v>
+        <v>45.18</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.385</v>
       </c>
       <c r="N12" t="n">
-        <v>45.60749999999999</v>
+        <v>45.6075</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.3875</v>
       </c>
       <c r="N13" t="n">
-        <v>46.53875</v>
+        <v>46.53874999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2423</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>888</v>
+      </c>
+      <c r="D75" t="n">
+        <v>396</v>
+      </c>
+      <c r="E75" t="n">
+        <v>491</v>
+      </c>
+      <c r="F75" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>212</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.90%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>226</v>
+      </c>
+      <c r="K75" t="n">
+        <v>174</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.85375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.07692307692307698</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8499999999999943</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0151272468410748</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6699999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.264150943396226</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.1799999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.00324207492795392</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
